--- a/SGC-CKN/Excel/880f830c-cb4e-4030-82c4-018617626a12_Phường_Hạc_Thành__tỉnh_Thanh_Hóa_P7-85_D800_11-03-2026.xlsx
+++ b/SGC-CKN/Excel/880f830c-cb4e-4030-82c4-018617626a12_Phường_Hạc_Thành__tỉnh_Thanh_Hóa_P7-85_D800_11-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
   <si>
     <t>Dự án</t>
   </si>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Đất san lấp</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">06:00
@@ -109,27 +109,27 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">06:30
 11/03/2026</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
-  </si>
-  <si>
     <t xml:space="preserve">08:00
 11/03/2026</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Sét xám trắng, xám xanh TT dẻo chảy</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh TT dẻo chảy</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">09:00
@@ -139,7 +139,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng, xám xanh TT nửa cứng</t>
+    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi san, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">09:30
@@ -149,7 +149,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi san, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:00
@@ -159,7 +159,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:00
@@ -169,33 +169,23 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">12:00
 11/03/2026</t>
   </si>
   <si>
+    <t>Chạm sỏi</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
-    <t>Cát xám, xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:00
-11/03/2026</t>
-  </si>
-  <si>
-    <t>Chạm sỏi</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Sỏi, xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:10
 11/03/2026</t>
   </si>
   <si>
@@ -236,7 +226,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -314,17 +304,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF134E4A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -335,7 +314,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,7 +343,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -374,7 +353,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -410,16 +389,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99F6E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -515,7 +484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -616,25 +585,13 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -660,7 +617,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -1020,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1220,19 +1177,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-1.227</v>
+        <v>-2</v>
       </c>
       <c r="G11" s="5">
-        <v>-2</v>
+        <v>-8.5</v>
       </c>
       <c r="H11" s="5">
         <v>0.25</v>
       </c>
       <c r="I11" s="5">
-        <v>0.77</v>
+        <v>6.5</v>
       </c>
       <c r="J11" s="8">
-        <v>3.09</v>
+        <v>26</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>9</v>
@@ -1249,25 +1206,25 @@
         <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-2</v>
+        <v>-8.5</v>
       </c>
       <c r="G12" s="9">
-        <v>-8.5</v>
+        <v>-10.5</v>
       </c>
       <c r="H12" s="9">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="I12" s="9">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="J12" s="12">
-        <v>26</v>
+        <v>1.33</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>9</v>
@@ -1275,34 +1232,34 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F13" s="13">
-        <v>-8.5</v>
+        <v>-10.5</v>
       </c>
       <c r="G13" s="13">
-        <v>-10.5</v>
+        <v>-18.6</v>
       </c>
       <c r="H13" s="13">
         <v>1.5</v>
       </c>
       <c r="I13" s="13">
-        <v>2</v>
+        <v>8.1</v>
       </c>
       <c r="J13" s="8">
-        <v>1.33</v>
+        <v>5.4</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>9</v>
@@ -1319,25 +1276,25 @@
         <v>37</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>38</v>
       </c>
       <c r="F14" s="16">
-        <v>-10.5</v>
+        <v>-18.6</v>
       </c>
       <c r="G14" s="16">
-        <v>-18.6</v>
+        <v>-22.7</v>
       </c>
       <c r="H14" s="16">
         <v>1</v>
       </c>
       <c r="I14" s="16">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="J14" s="12">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>9</v>
@@ -1360,19 +1317,19 @@
         <v>41</v>
       </c>
       <c r="F15" s="19">
-        <v>-18.6</v>
+        <v>-22.7</v>
       </c>
       <c r="G15" s="19">
-        <v>-22.7</v>
+        <v>-26.6</v>
       </c>
       <c r="H15" s="19">
         <v>0.5</v>
       </c>
       <c r="I15" s="19">
-        <v>4.1</v>
-      </c>
-      <c r="J15" s="12">
-        <v>8.2</v>
+        <v>3.9</v>
+      </c>
+      <c r="J15" s="8">
+        <v>7.8</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>9</v>
@@ -1395,19 +1352,19 @@
         <v>44</v>
       </c>
       <c r="F16" s="22">
-        <v>-22.7</v>
+        <v>-26.6</v>
       </c>
       <c r="G16" s="22">
-        <v>-26.6</v>
+        <v>-36.8</v>
       </c>
       <c r="H16" s="22">
         <v>0.5</v>
       </c>
       <c r="I16" s="22">
-        <v>3.9</v>
-      </c>
-      <c r="J16" s="12">
-        <v>7.8</v>
+        <v>10.2</v>
+      </c>
+      <c r="J16" s="8">
+        <v>20.4</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>9</v>
@@ -1430,19 +1387,19 @@
         <v>47</v>
       </c>
       <c r="F17" s="25">
-        <v>-26.6</v>
+        <v>-36.8</v>
       </c>
       <c r="G17" s="25">
-        <v>-36.8</v>
+        <v>-39.24</v>
       </c>
       <c r="H17" s="25">
         <v>1</v>
       </c>
       <c r="I17" s="25">
-        <v>10.2</v>
+        <v>2.44</v>
       </c>
       <c r="J17" s="12">
-        <v>10.2</v>
+        <v>2.44</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>9</v>
@@ -1465,109 +1422,75 @@
         <v>50</v>
       </c>
       <c r="F18" s="28">
-        <v>-36.8</v>
+        <v>-39.24</v>
       </c>
       <c r="G18" s="28">
-        <v>-39.24</v>
+        <v>-40.65</v>
       </c>
       <c r="H18" s="28">
         <v>1</v>
       </c>
       <c r="I18" s="28">
-        <v>2.44</v>
-      </c>
-      <c r="J18" s="8">
-        <v>2.44</v>
+        <v>1.41</v>
+      </c>
+      <c r="J18" s="12">
+        <v>1.41</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>50</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F19" s="31">
-        <v>-39.24</v>
+        <v>-40.65</v>
       </c>
       <c r="G19" s="31">
-        <v>-40.65</v>
+        <v>-45.05</v>
       </c>
       <c r="H19" s="31">
         <v>2</v>
       </c>
       <c r="I19" s="31">
-        <v>1.41</v>
-      </c>
-      <c r="J19" s="34">
-        <v>0.7</v>
+        <v>4.4</v>
+      </c>
+      <c r="J19" s="12">
+        <v>2.2</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="36" t="s">
+    </row>
+    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" s="35">
-        <v>-40.65</v>
-      </c>
-      <c r="G20" s="35">
-        <v>-45.05</v>
-      </c>
-      <c r="H20" s="35">
-        <v>0.17</v>
-      </c>
-      <c r="I20" s="35">
-        <v>4.4</v>
-      </c>
-      <c r="J20" s="12">
-        <v>26.4</v>
-      </c>
-      <c r="K20" s="36" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-    </row>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1627,7 +1550,6 @@
     <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -1638,7 +1560,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A22:K22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1648,7 +1570,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1661,31 +1583,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1702,19 +1624,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-1.23</v>
+        <v>-2</v>
       </c>
       <c r="F2" s="5">
-        <v>-2</v>
+        <v>-8.5</v>
       </c>
       <c r="G2" s="5">
         <v>0.25</v>
       </c>
       <c r="H2" s="5">
-        <v>0.77</v>
+        <v>6.5</v>
       </c>
       <c r="I2" s="8">
-        <v>3.09</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1731,19 +1653,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-2</v>
+        <v>-8.5</v>
       </c>
       <c r="F3" s="9">
-        <v>-8.5</v>
+        <v>-10.5</v>
       </c>
       <c r="G3" s="9">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="H3" s="9">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="I3" s="12">
-        <v>26</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1754,25 +1676,25 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
       </c>
       <c r="E4" s="13">
-        <v>-8.5</v>
+        <v>-10.5</v>
       </c>
       <c r="F4" s="13">
-        <v>-10.5</v>
+        <v>-18.6</v>
       </c>
       <c r="G4" s="13">
         <v>1.5</v>
       </c>
       <c r="H4" s="13">
-        <v>2</v>
+        <v>8.1</v>
       </c>
       <c r="I4" s="8">
-        <v>1.33</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1789,19 +1711,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-10.5</v>
+        <v>-18.6</v>
       </c>
       <c r="F5" s="16">
-        <v>-18.6</v>
+        <v>-22.7</v>
       </c>
       <c r="G5" s="16">
         <v>1</v>
       </c>
       <c r="H5" s="16">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="I5" s="12">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1818,19 +1740,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-18.6</v>
+        <v>-22.7</v>
       </c>
       <c r="F6" s="19">
-        <v>-22.7</v>
+        <v>-26.6</v>
       </c>
       <c r="G6" s="19">
         <v>0.5</v>
       </c>
       <c r="H6" s="19">
-        <v>4.1</v>
-      </c>
-      <c r="I6" s="12">
-        <v>8.2</v>
+        <v>3.9</v>
+      </c>
+      <c r="I6" s="8">
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1847,19 +1769,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-22.7</v>
+        <v>-26.6</v>
       </c>
       <c r="F7" s="22">
-        <v>-26.6</v>
+        <v>-36.8</v>
       </c>
       <c r="G7" s="22">
         <v>0.5</v>
       </c>
       <c r="H7" s="22">
-        <v>3.9</v>
-      </c>
-      <c r="I7" s="12">
-        <v>7.8</v>
+        <v>10.2</v>
+      </c>
+      <c r="I7" s="8">
+        <v>20.4</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1876,19 +1798,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-26.6</v>
+        <v>-36.8</v>
       </c>
       <c r="F8" s="25">
-        <v>-36.8</v>
+        <v>-39.24</v>
       </c>
       <c r="G8" s="25">
         <v>1</v>
       </c>
       <c r="H8" s="25">
-        <v>10.2</v>
+        <v>2.44</v>
       </c>
       <c r="I8" s="12">
-        <v>10.2</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1905,19 +1827,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-36.8</v>
+        <v>-39.24</v>
       </c>
       <c r="F9" s="28">
-        <v>-39.24</v>
+        <v>-40.65</v>
       </c>
       <c r="G9" s="28">
         <v>1</v>
       </c>
       <c r="H9" s="28">
-        <v>2.44</v>
-      </c>
-      <c r="I9" s="8">
-        <v>2.44</v>
+        <v>1.41</v>
+      </c>
+      <c r="I9" s="12">
+        <v>1.41</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1928,83 +1850,54 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-39.24</v>
+        <v>-40.65</v>
       </c>
       <c r="F10" s="31">
-        <v>-40.65</v>
+        <v>-45.05</v>
       </c>
       <c r="G10" s="31">
         <v>2</v>
       </c>
       <c r="H10" s="31">
-        <v>1.41</v>
-      </c>
-      <c r="I10" s="34">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
-        <v>10</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>11</v>
+        <v>4.4</v>
+      </c>
+      <c r="I10" s="12">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>9</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="35">
-        <v>1</v>
-      </c>
-      <c r="E11" s="35">
-        <v>-40.65</v>
-      </c>
-      <c r="F11" s="35">
+        <v>9</v>
+      </c>
+      <c r="D11" s="36">
+        <v>9</v>
+      </c>
+      <c r="E11" s="36">
+        <v>-2</v>
+      </c>
+      <c r="F11" s="36">
         <v>-45.05</v>
       </c>
-      <c r="G11" s="35">
-        <v>0.17</v>
-      </c>
-      <c r="H11" s="35">
-        <v>4.4</v>
-      </c>
-      <c r="I11" s="12">
-        <v>26.4</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="40">
-        <v>10</v>
-      </c>
-      <c r="E12" s="40">
-        <v>-1.23</v>
-      </c>
-      <c r="F12" s="40">
-        <v>-45.05</v>
-      </c>
-      <c r="G12" s="40">
-        <v>8.17</v>
-      </c>
-      <c r="H12" s="40">
-        <v>43.82</v>
-      </c>
-      <c r="I12" s="40">
-        <v>5.37</v>
+      <c r="G11" s="36">
+        <v>9.25</v>
+      </c>
+      <c r="H11" s="36">
+        <v>43.05</v>
+      </c>
+      <c r="I11" s="36">
+        <v>4.65</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/880f830c-cb4e-4030-82c4-018617626a12_Phường_Hạc_Thành__tỉnh_Thanh_Hóa_P7-85_D800_11-03-2026.xlsx
+++ b/SGC-CKN/Excel/880f830c-cb4e-4030-82c4-018617626a12_Phường_Hạc_Thành__tỉnh_Thanh_Hóa_P7-85_D800_11-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="64">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P7-85</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t/>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>SGCT-KCN0004</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">06:00
@@ -106,10 +106,13 @@
 11/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">06:30
@@ -123,13 +126,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh TT dẻo chảy</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng, xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">09:00
@@ -139,7 +139,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi san, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">09:30
@@ -149,9 +149,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">10:00
 11/03/2026</t>
   </si>
@@ -159,7 +156,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:00
@@ -180,9 +177,6 @@
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>Sỏi, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:00
@@ -226,7 +220,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -297,11 +291,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF831843"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -314,7 +303,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -384,11 +373,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBCFE8"/>
       </patternFill>
     </fill>
     <fill>
@@ -484,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -576,22 +560,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1192,24 +1167,24 @@
         <v>26</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-8.5</v>
@@ -1227,24 +1202,24 @@
         <v>1.33</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F13" s="13">
         <v>-10.5</v>
@@ -1262,7 +1237,7 @@
         <v>5.4</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1276,7 +1251,7 @@
         <v>37</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>38</v>
@@ -1297,7 +1272,7 @@
         <v>4.1</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1332,163 +1307,163 @@
         <v>7.8</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="22">
+      <c r="F16" s="19">
         <v>-26.6</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="19">
         <v>-36.8</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="19">
         <v>0.5</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="19">
         <v>10.2</v>
       </c>
       <c r="J16" s="8">
         <v>20.4</v>
       </c>
-      <c r="K16" s="23" t="s">
-        <v>9</v>
+      <c r="K16" s="20" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="D17" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="F17" s="22">
         <v>-36.8</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="22">
         <v>-39.24</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="22">
         <v>1</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="22">
         <v>2.44</v>
       </c>
       <c r="J17" s="12">
         <v>2.44</v>
       </c>
-      <c r="K17" s="26" t="s">
-        <v>9</v>
+      <c r="K17" s="23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="28">
+      <c r="F18" s="25">
         <v>-39.24</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="25">
         <v>-40.65</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="25">
         <v>1</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="25">
         <v>1.41</v>
       </c>
       <c r="J18" s="12">
         <v>1.41</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K18" s="26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="B19" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="31">
+      <c r="F19" s="28">
         <v>-40.65</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="28">
         <v>-45.05</v>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="28">
         <v>2</v>
       </c>
-      <c r="I19" s="31">
+      <c r="I19" s="28">
         <v>4.4</v>
       </c>
       <c r="J19" s="12">
         <v>2.2</v>
       </c>
-      <c r="K19" s="32" t="s">
-        <v>55</v>
+      <c r="K19" s="29" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
+      <c r="A22" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
     </row>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1570,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1583,31 +1558,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1647,7 +1622,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1676,7 +1651,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1737,22 +1712,22 @@
         <v>40</v>
       </c>
       <c r="D6" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="19">
         <v>-22.7</v>
       </c>
       <c r="F6" s="19">
-        <v>-26.6</v>
+        <v>-36.8</v>
       </c>
       <c r="G6" s="19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H6" s="19">
-        <v>3.9</v>
+        <v>14.1</v>
       </c>
       <c r="I6" s="8">
-        <v>7.8</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1763,25 +1738,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-26.6</v>
+        <v>-36.8</v>
       </c>
       <c r="F7" s="22">
-        <v>-36.8</v>
+        <v>-39.24</v>
       </c>
       <c r="G7" s="22">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H7" s="22">
-        <v>10.2</v>
-      </c>
-      <c r="I7" s="8">
-        <v>20.4</v>
+        <v>2.44</v>
+      </c>
+      <c r="I7" s="12">
+        <v>2.44</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1792,25 +1767,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-36.8</v>
+        <v>-39.24</v>
       </c>
       <c r="F8" s="25">
-        <v>-39.24</v>
+        <v>-40.65</v>
       </c>
       <c r="G8" s="25">
         <v>1</v>
       </c>
       <c r="H8" s="25">
-        <v>2.44</v>
+        <v>1.41</v>
       </c>
       <c r="I8" s="12">
-        <v>2.44</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1821,82 +1796,53 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-39.24</v>
+        <v>-40.65</v>
       </c>
       <c r="F9" s="28">
-        <v>-40.65</v>
+        <v>-45.05</v>
       </c>
       <c r="G9" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="28">
-        <v>1.41</v>
+        <v>4.4</v>
       </c>
       <c r="I9" s="12">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="31">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="33">
         <v>9</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="31">
-        <v>1</v>
-      </c>
-      <c r="E10" s="31">
-        <v>-40.65</v>
-      </c>
-      <c r="F10" s="31">
+      <c r="E10" s="33">
+        <v>-2</v>
+      </c>
+      <c r="F10" s="33">
         <v>-45.05</v>
       </c>
-      <c r="G10" s="31">
-        <v>2</v>
-      </c>
-      <c r="H10" s="31">
-        <v>4.4</v>
-      </c>
-      <c r="I10" s="12">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="36">
-        <v>9</v>
-      </c>
-      <c r="E11" s="36">
-        <v>-2</v>
-      </c>
-      <c r="F11" s="36">
-        <v>-45.05</v>
-      </c>
-      <c r="G11" s="36">
+      <c r="G10" s="33">
         <v>9.25</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H10" s="33">
         <v>43.05</v>
       </c>
-      <c r="I11" s="36">
+      <c r="I10" s="33">
         <v>4.65</v>
       </c>
     </row>
